--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467625</v>
+        <v>120467540</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519277</v>
+        <v>519268</v>
       </c>
       <c r="R2" t="n">
-        <v>7034510</v>
+        <v>7034553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467547</v>
+        <v>120467543</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519276</v>
+        <v>519241</v>
       </c>
       <c r="R4" t="n">
-        <v>7034508</v>
+        <v>7034507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467551</v>
+        <v>120467608</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519324</v>
+        <v>519308</v>
       </c>
       <c r="R5" t="n">
-        <v>7034551</v>
+        <v>7034634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467533</v>
+        <v>120467552</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519292</v>
+        <v>519423</v>
       </c>
       <c r="R6" t="n">
-        <v>7034702</v>
+        <v>7034575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467548</v>
+        <v>120467539</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519263</v>
+        <v>519273</v>
       </c>
       <c r="R7" t="n">
-        <v>7034516</v>
+        <v>7034556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467546</v>
+        <v>120467550</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519254</v>
+        <v>519263</v>
       </c>
       <c r="R8" t="n">
-        <v>7034484</v>
+        <v>7034520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467538</v>
+        <v>120467545</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519248</v>
+        <v>519234</v>
       </c>
       <c r="R9" t="n">
-        <v>7034653</v>
+        <v>7034493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467544</v>
+        <v>120467546</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519233</v>
+        <v>519254</v>
       </c>
       <c r="R10" t="n">
-        <v>7034494</v>
+        <v>7034484</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467541</v>
+        <v>120467538</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519253</v>
+        <v>519248</v>
       </c>
       <c r="R11" t="n">
-        <v>7034553</v>
+        <v>7034653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467549</v>
+        <v>120467604</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,34 +1756,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519261</v>
+        <v>519274</v>
       </c>
       <c r="R12" t="n">
-        <v>7034519</v>
+        <v>7034556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1828,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>5 st +</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467531</v>
+        <v>120467536</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519310</v>
+        <v>519272</v>
       </c>
       <c r="R13" t="n">
-        <v>7034724</v>
+        <v>7034688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467543</v>
+        <v>120467534</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519241</v>
+        <v>519291</v>
       </c>
       <c r="R14" t="n">
-        <v>7034507</v>
+        <v>7034683</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2042,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467537</v>
+        <v>120467622</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519258</v>
+        <v>519351</v>
       </c>
       <c r="R15" t="n">
-        <v>7034685</v>
+        <v>7034684</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2145,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2171,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467552</v>
+        <v>120467533</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519423</v>
+        <v>519292</v>
       </c>
       <c r="R16" t="n">
-        <v>7034575</v>
+        <v>7034702</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467608</v>
+        <v>120467605</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>91277</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2290,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519308</v>
+        <v>519237</v>
       </c>
       <c r="R17" t="n">
-        <v>7034634</v>
+        <v>7034632</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2380,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467532</v>
+        <v>120467544</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519303</v>
+        <v>519233</v>
       </c>
       <c r="R18" t="n">
-        <v>7034701</v>
+        <v>7034494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2460,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2487,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467550</v>
+        <v>120467531</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2524,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519263</v>
+        <v>519310</v>
       </c>
       <c r="R19" t="n">
-        <v>7034520</v>
+        <v>7034724</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2567,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2701,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467540</v>
+        <v>120467549</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519268</v>
+        <v>519261</v>
       </c>
       <c r="R21" t="n">
-        <v>7034553</v>
+        <v>7034519</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2781,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2808,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467534</v>
+        <v>120467529</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519291</v>
+        <v>519418</v>
       </c>
       <c r="R22" t="n">
-        <v>7034683</v>
+        <v>7034598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2888,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467604</v>
+        <v>120467625</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,42 +2931,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519274</v>
+        <v>519277</v>
       </c>
       <c r="R23" t="n">
-        <v>7034556</v>
+        <v>7034510</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,11 +2991,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 st +</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,7 +3017,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467536</v>
+        <v>120467537</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3067,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519272</v>
+        <v>519258</v>
       </c>
       <c r="R24" t="n">
-        <v>7034688</v>
+        <v>7034685</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467622</v>
+        <v>120467547</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,21 +3140,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519351</v>
+        <v>519276</v>
       </c>
       <c r="R25" t="n">
-        <v>7034684</v>
+        <v>7034508</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,6 +3200,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467545</v>
+        <v>120467548</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3276,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519234</v>
+        <v>519263</v>
       </c>
       <c r="R26" t="n">
-        <v>7034493</v>
+        <v>7034516</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3343,7 +3338,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467539</v>
+        <v>120467532</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3383,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519273</v>
+        <v>519303</v>
       </c>
       <c r="R27" t="n">
-        <v>7034556</v>
+        <v>7034701</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3423,7 +3418,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467605</v>
+        <v>120467541</v>
       </c>
       <c r="B28" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,25 +3457,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3490,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519237</v>
+        <v>519253</v>
       </c>
       <c r="R28" t="n">
-        <v>7034632</v>
+        <v>7034553</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3526,6 +3521,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,7 +3552,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467529</v>
+        <v>120467551</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519418</v>
+        <v>519324</v>
       </c>
       <c r="R29" t="n">
-        <v>7034598</v>
+        <v>7034551</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467540</v>
+        <v>120467623</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519268</v>
+        <v>519234</v>
       </c>
       <c r="R2" t="n">
-        <v>7034553</v>
+        <v>7034600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467542</v>
+        <v>120467604</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519242</v>
+        <v>519274</v>
       </c>
       <c r="R3" t="n">
-        <v>7034507</v>
+        <v>7034556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>5 st +</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467543</v>
+        <v>120467608</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519241</v>
+        <v>519308</v>
       </c>
       <c r="R4" t="n">
-        <v>7034507</v>
+        <v>7034634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467608</v>
+        <v>120467605</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519308</v>
+        <v>519237</v>
       </c>
       <c r="R5" t="n">
-        <v>7034634</v>
+        <v>7034632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467552</v>
+        <v>120467551</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519423</v>
+        <v>519324</v>
       </c>
       <c r="R6" t="n">
-        <v>7034575</v>
+        <v>7034551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467539</v>
+        <v>120467550</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519273</v>
+        <v>519263</v>
       </c>
       <c r="R7" t="n">
-        <v>7034556</v>
+        <v>7034520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1310,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467550</v>
+        <v>120467529</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519263</v>
+        <v>519418</v>
       </c>
       <c r="R8" t="n">
-        <v>7034520</v>
+        <v>7034598</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1390,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467545</v>
+        <v>120467542</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519234</v>
+        <v>519242</v>
       </c>
       <c r="R9" t="n">
-        <v>7034493</v>
+        <v>7034507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467546</v>
+        <v>120467622</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519254</v>
+        <v>519351</v>
       </c>
       <c r="R10" t="n">
-        <v>7034484</v>
+        <v>7034684</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1600,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467538</v>
+        <v>120467541</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519248</v>
+        <v>519253</v>
       </c>
       <c r="R11" t="n">
-        <v>7034653</v>
+        <v>7034553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1706,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467604</v>
+        <v>120467552</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,42 +1749,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519274</v>
+        <v>519423</v>
       </c>
       <c r="R12" t="n">
-        <v>7034556</v>
+        <v>7034575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 st +</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467536</v>
+        <v>120467533</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1895,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519272</v>
+        <v>519292</v>
       </c>
       <c r="R13" t="n">
-        <v>7034688</v>
+        <v>7034702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467534</v>
+        <v>120467547</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2002,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519291</v>
+        <v>519276</v>
       </c>
       <c r="R14" t="n">
-        <v>7034683</v>
+        <v>7034508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2027,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467622</v>
+        <v>120467543</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519351</v>
+        <v>519241</v>
       </c>
       <c r="R15" t="n">
-        <v>7034684</v>
+        <v>7034507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467533</v>
+        <v>120467530</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2211,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519292</v>
+        <v>519381</v>
       </c>
       <c r="R16" t="n">
-        <v>7034702</v>
+        <v>7034632</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2241,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467605</v>
+        <v>120467625</v>
       </c>
       <c r="B17" t="n">
-        <v>91277</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,25 +2280,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519237</v>
+        <v>519277</v>
       </c>
       <c r="R17" t="n">
-        <v>7034632</v>
+        <v>7034510</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2370,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467544</v>
+        <v>120467539</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2420,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519233</v>
+        <v>519273</v>
       </c>
       <c r="R18" t="n">
-        <v>7034494</v>
+        <v>7034556</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467531</v>
+        <v>120467532</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519310</v>
+        <v>519303</v>
       </c>
       <c r="R19" t="n">
-        <v>7034724</v>
+        <v>7034701</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2584,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467530</v>
+        <v>120467546</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2634,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519381</v>
+        <v>519254</v>
       </c>
       <c r="R20" t="n">
-        <v>7034632</v>
+        <v>7034484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2691,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467549</v>
+        <v>120467536</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2741,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519261</v>
+        <v>519272</v>
       </c>
       <c r="R21" t="n">
-        <v>7034519</v>
+        <v>7034688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,7 +2771,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,7 +2798,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467529</v>
+        <v>120467548</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2848,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519418</v>
+        <v>519263</v>
       </c>
       <c r="R22" t="n">
-        <v>7034598</v>
+        <v>7034516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,7 +2878,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2915,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467625</v>
+        <v>120467531</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2931,21 +2921,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519277</v>
+        <v>519310</v>
       </c>
       <c r="R23" t="n">
-        <v>7034510</v>
+        <v>7034724</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,6 +2981,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,7 +3012,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467537</v>
+        <v>120467540</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3057,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519258</v>
+        <v>519268</v>
       </c>
       <c r="R24" t="n">
-        <v>7034685</v>
+        <v>7034553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467547</v>
+        <v>120467538</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519276</v>
+        <v>519248</v>
       </c>
       <c r="R25" t="n">
-        <v>7034508</v>
+        <v>7034653</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3199,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,7 +3226,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467548</v>
+        <v>120467545</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519263</v>
+        <v>519234</v>
       </c>
       <c r="R26" t="n">
-        <v>7034516</v>
+        <v>7034493</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467532</v>
+        <v>120467549</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3378,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519303</v>
+        <v>519261</v>
       </c>
       <c r="R27" t="n">
-        <v>7034701</v>
+        <v>7034519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,7 +3440,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467541</v>
+        <v>120467534</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519253</v>
+        <v>519291</v>
       </c>
       <c r="R28" t="n">
-        <v>7034553</v>
+        <v>7034683</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3552,7 +3547,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467551</v>
+        <v>120467544</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519324</v>
+        <v>519233</v>
       </c>
       <c r="R29" t="n">
-        <v>7034551</v>
+        <v>7034494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3659,10 +3654,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467623</v>
+        <v>120467537</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,21 +3670,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3699,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519234</v>
+        <v>519258</v>
       </c>
       <c r="R30" t="n">
-        <v>7034600</v>
+        <v>7034685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,6 +3730,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467623</v>
+        <v>120467548</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519234</v>
+        <v>519263</v>
       </c>
       <c r="R2" t="n">
-        <v>7034600</v>
+        <v>7034516</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467604</v>
+        <v>120467537</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519274</v>
+        <v>519258</v>
       </c>
       <c r="R3" t="n">
-        <v>7034556</v>
+        <v>7034685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5 st +</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467608</v>
+        <v>120467605</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>91277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519308</v>
+        <v>519237</v>
       </c>
       <c r="R4" t="n">
-        <v>7034634</v>
+        <v>7034632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467605</v>
+        <v>120467538</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519237</v>
+        <v>519248</v>
       </c>
       <c r="R5" t="n">
-        <v>7034632</v>
+        <v>7034653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467551</v>
+        <v>120467623</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519324</v>
+        <v>519234</v>
       </c>
       <c r="R6" t="n">
-        <v>7034551</v>
+        <v>7034600</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467550</v>
+        <v>120467531</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1243,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519263</v>
+        <v>519310</v>
       </c>
       <c r="R7" t="n">
-        <v>7034520</v>
+        <v>7034724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467529</v>
+        <v>120467608</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519418</v>
+        <v>519308</v>
       </c>
       <c r="R8" t="n">
-        <v>7034598</v>
+        <v>7034634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467542</v>
+        <v>120467622</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519242</v>
+        <v>519351</v>
       </c>
       <c r="R9" t="n">
-        <v>7034507</v>
+        <v>7034684</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467622</v>
+        <v>120467545</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519351</v>
+        <v>519234</v>
       </c>
       <c r="R10" t="n">
-        <v>7034684</v>
+        <v>7034493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467541</v>
+        <v>120467536</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1666,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519253</v>
+        <v>519272</v>
       </c>
       <c r="R11" t="n">
-        <v>7034553</v>
+        <v>7034688</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467552</v>
+        <v>120467543</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1773,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519423</v>
+        <v>519241</v>
       </c>
       <c r="R12" t="n">
-        <v>7034575</v>
+        <v>7034507</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467547</v>
+        <v>120467540</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1987,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519276</v>
+        <v>519268</v>
       </c>
       <c r="R14" t="n">
-        <v>7034508</v>
+        <v>7034553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467543</v>
+        <v>120467542</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2094,7 +2086,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519241</v>
+        <v>519242</v>
       </c>
       <c r="R15" t="n">
         <v>7034507</v>
@@ -2134,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467530</v>
+        <v>120467604</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,34 +2169,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519381</v>
+        <v>519274</v>
       </c>
       <c r="R16" t="n">
-        <v>7034632</v>
+        <v>7034556</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>5 st +</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467625</v>
+        <v>120467544</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519277</v>
+        <v>519233</v>
       </c>
       <c r="R17" t="n">
-        <v>7034510</v>
+        <v>7034494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,6 +2344,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,7 +2375,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467539</v>
+        <v>120467546</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2410,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519273</v>
+        <v>519254</v>
       </c>
       <c r="R18" t="n">
-        <v>7034556</v>
+        <v>7034484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2455,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,7 +2482,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467532</v>
+        <v>120467534</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519303</v>
+        <v>519291</v>
       </c>
       <c r="R19" t="n">
-        <v>7034701</v>
+        <v>7034683</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,7 +2589,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467546</v>
+        <v>120467529</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2624,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519254</v>
+        <v>519418</v>
       </c>
       <c r="R20" t="n">
-        <v>7034484</v>
+        <v>7034598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2696,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467536</v>
+        <v>120467551</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2731,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519272</v>
+        <v>519324</v>
       </c>
       <c r="R21" t="n">
-        <v>7034688</v>
+        <v>7034551</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,7 +2776,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,7 +2803,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467548</v>
+        <v>120467532</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2838,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519263</v>
+        <v>519303</v>
       </c>
       <c r="R22" t="n">
-        <v>7034516</v>
+        <v>7034701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467531</v>
+        <v>120467625</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519310</v>
+        <v>519277</v>
       </c>
       <c r="R23" t="n">
-        <v>7034724</v>
+        <v>7034510</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,11 +2986,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,7 +3012,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467540</v>
+        <v>120467541</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519268</v>
+        <v>519253</v>
       </c>
       <c r="R24" t="n">
         <v>7034553</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467538</v>
+        <v>120467547</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519248</v>
+        <v>519276</v>
       </c>
       <c r="R25" t="n">
-        <v>7034653</v>
+        <v>7034508</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,7 +3226,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467545</v>
+        <v>120467530</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519234</v>
+        <v>519381</v>
       </c>
       <c r="R26" t="n">
-        <v>7034493</v>
+        <v>7034632</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467549</v>
+        <v>120467552</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519261</v>
+        <v>519423</v>
       </c>
       <c r="R27" t="n">
-        <v>7034519</v>
+        <v>7034575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467534</v>
+        <v>120467550</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519291</v>
+        <v>519263</v>
       </c>
       <c r="R28" t="n">
-        <v>7034683</v>
+        <v>7034520</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467544</v>
+        <v>120467539</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519233</v>
+        <v>519273</v>
       </c>
       <c r="R29" t="n">
-        <v>7034494</v>
+        <v>7034556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467537</v>
+        <v>120467549</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519258</v>
+        <v>519261</v>
       </c>
       <c r="R30" t="n">
-        <v>7034685</v>
+        <v>7034519</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467548</v>
+        <v>120467541</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519263</v>
+        <v>519253</v>
       </c>
       <c r="R2" t="n">
-        <v>7034516</v>
+        <v>7034553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467537</v>
+        <v>120467539</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519258</v>
+        <v>519273</v>
       </c>
       <c r="R3" t="n">
-        <v>7034685</v>
+        <v>7034556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467605</v>
+        <v>120467545</v>
       </c>
       <c r="B4" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519237</v>
+        <v>519234</v>
       </c>
       <c r="R4" t="n">
-        <v>7034632</v>
+        <v>7034493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467538</v>
+        <v>120467625</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519248</v>
+        <v>519277</v>
       </c>
       <c r="R5" t="n">
-        <v>7034653</v>
+        <v>7034510</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467623</v>
+        <v>120467546</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519234</v>
+        <v>519254</v>
       </c>
       <c r="R6" t="n">
-        <v>7034600</v>
+        <v>7034484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467531</v>
+        <v>120467549</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519310</v>
+        <v>519261</v>
       </c>
       <c r="R7" t="n">
-        <v>7034724</v>
+        <v>7034519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467608</v>
+        <v>120467529</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519308</v>
+        <v>519418</v>
       </c>
       <c r="R8" t="n">
-        <v>7034634</v>
+        <v>7034598</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467622</v>
+        <v>120467548</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519351</v>
+        <v>519263</v>
       </c>
       <c r="R9" t="n">
-        <v>7034684</v>
+        <v>7034516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467545</v>
+        <v>120467536</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1551,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519234</v>
+        <v>519272</v>
       </c>
       <c r="R10" t="n">
-        <v>7034493</v>
+        <v>7034688</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467536</v>
+        <v>120467544</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1658,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519272</v>
+        <v>519233</v>
       </c>
       <c r="R11" t="n">
-        <v>7034688</v>
+        <v>7034494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467543</v>
+        <v>120467537</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1765,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519241</v>
+        <v>519258</v>
       </c>
       <c r="R12" t="n">
-        <v>7034507</v>
+        <v>7034685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467533</v>
+        <v>120467543</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1872,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519292</v>
+        <v>519241</v>
       </c>
       <c r="R13" t="n">
-        <v>7034702</v>
+        <v>7034507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467540</v>
+        <v>120467605</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>91277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519268</v>
+        <v>519237</v>
       </c>
       <c r="R14" t="n">
-        <v>7034553</v>
+        <v>7034632</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467542</v>
+        <v>120467532</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519242</v>
+        <v>519303</v>
       </c>
       <c r="R15" t="n">
-        <v>7034507</v>
+        <v>7034701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467604</v>
+        <v>120467542</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,42 +2179,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519274</v>
+        <v>519242</v>
       </c>
       <c r="R16" t="n">
-        <v>7034556</v>
+        <v>7034507</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>5 st +</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467544</v>
+        <v>120467538</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2308,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519233</v>
+        <v>519248</v>
       </c>
       <c r="R17" t="n">
-        <v>7034494</v>
+        <v>7034653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2348,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467546</v>
+        <v>120467551</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2415,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519254</v>
+        <v>519324</v>
       </c>
       <c r="R18" t="n">
-        <v>7034484</v>
+        <v>7034551</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467534</v>
+        <v>120467547</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2522,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519291</v>
+        <v>519276</v>
       </c>
       <c r="R19" t="n">
-        <v>7034683</v>
+        <v>7034508</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467529</v>
+        <v>120467540</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2629,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519418</v>
+        <v>519268</v>
       </c>
       <c r="R20" t="n">
-        <v>7034598</v>
+        <v>7034553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467551</v>
+        <v>120467533</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2736,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519324</v>
+        <v>519292</v>
       </c>
       <c r="R21" t="n">
-        <v>7034551</v>
+        <v>7034702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467532</v>
+        <v>120467608</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2843,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519303</v>
+        <v>519308</v>
       </c>
       <c r="R22" t="n">
-        <v>7034701</v>
+        <v>7034634</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467625</v>
+        <v>120467623</v>
       </c>
       <c r="B23" t="n">
         <v>90598</v>
@@ -2950,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519277</v>
+        <v>519234</v>
       </c>
       <c r="R23" t="n">
-        <v>7034510</v>
+        <v>7034600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467541</v>
+        <v>120467552</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3052,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519253</v>
+        <v>519423</v>
       </c>
       <c r="R24" t="n">
-        <v>7034553</v>
+        <v>7034575</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467547</v>
+        <v>120467604</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,34 +3132,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519276</v>
+        <v>519274</v>
       </c>
       <c r="R25" t="n">
-        <v>7034508</v>
+        <v>7034556</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3204,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>5 st +</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,7 +3338,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467552</v>
+        <v>120467531</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3373,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519423</v>
+        <v>519310</v>
       </c>
       <c r="R27" t="n">
-        <v>7034575</v>
+        <v>7034724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,7 +3552,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467539</v>
+        <v>120467534</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3587,10 +3592,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519273</v>
+        <v>519291</v>
       </c>
       <c r="R29" t="n">
-        <v>7034556</v>
+        <v>7034683</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,10 +3659,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467549</v>
+        <v>120467622</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,21 +3675,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3699,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519261</v>
+        <v>519351</v>
       </c>
       <c r="R30" t="n">
-        <v>7034519</v>
+        <v>7034684</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3730,11 +3735,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467605</v>
+        <v>120467532</v>
       </c>
       <c r="B14" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519237</v>
+        <v>519303</v>
       </c>
       <c r="R14" t="n">
-        <v>7034632</v>
+        <v>7034701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467532</v>
+        <v>120467542</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519303</v>
+        <v>519242</v>
       </c>
       <c r="R15" t="n">
-        <v>7034701</v>
+        <v>7034507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467542</v>
+        <v>120467605</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2180,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519242</v>
+        <v>519237</v>
       </c>
       <c r="R16" t="n">
-        <v>7034507</v>
+        <v>7034632</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2244,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467540</v>
+        <v>120467608</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519268</v>
+        <v>519308</v>
       </c>
       <c r="R20" t="n">
-        <v>7034553</v>
+        <v>7034634</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,11 +2667,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467533</v>
+        <v>120467540</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519292</v>
+        <v>519268</v>
       </c>
       <c r="R21" t="n">
-        <v>7034702</v>
+        <v>7034553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467608</v>
+        <v>120467533</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519308</v>
+        <v>519292</v>
       </c>
       <c r="R22" t="n">
-        <v>7034634</v>
+        <v>7034702</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3759,6 +3759,411 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128047142</v>
+      </c>
+      <c r="B31" t="n">
+        <v>75127</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>519270</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7034532</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128047151</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75144</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>519394</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7034721</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128047102</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>519244</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7034471</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128047148</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Finnboriset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>519354</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7034679</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128047142</v>
       </c>
       <c r="B31" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128047151</v>
       </c>
       <c r="B32" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>98363</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128047142</v>
       </c>
       <c r="B31" t="n">
-        <v>75130</v>
+        <v>75136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128047151</v>
       </c>
       <c r="B32" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98363</v>
+        <v>98371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98371</v>
+        <v>98372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>98374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128047142</v>
       </c>
       <c r="B31" t="n">
-        <v>75136</v>
+        <v>75139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128047151</v>
       </c>
       <c r="B32" t="n">
-        <v>75153</v>
+        <v>75156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98374</v>
+        <v>98382</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128047142</v>
       </c>
       <c r="B31" t="n">
-        <v>75139</v>
+        <v>75154</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128047151</v>
       </c>
       <c r="B32" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98382</v>
+        <v>98475</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128047142</v>
       </c>
       <c r="B31" t="n">
-        <v>75154</v>
+        <v>75158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128047151</v>
       </c>
       <c r="B32" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128047102</v>
       </c>
       <c r="B33" t="n">
-        <v>98475</v>
+        <v>98489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>128047148</v>
       </c>
       <c r="B34" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120467551</v>
+        <v>120467605</v>
       </c>
       <c r="B2" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519324</v>
+        <v>519237</v>
       </c>
       <c r="R2" t="n">
-        <v>7034551</v>
+        <v>7034632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120467537</v>
+        <v>128047095</v>
       </c>
       <c r="B3" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519258</v>
+        <v>519507</v>
       </c>
       <c r="R3" t="n">
-        <v>7034685</v>
+        <v>7034546</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,71 +855,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120467533</v>
+        <v>128047142</v>
       </c>
       <c r="B4" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519292</v>
+        <v>519270</v>
       </c>
       <c r="R4" t="n">
-        <v>7034702</v>
+        <v>7034532</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,33 +956,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120467532</v>
+        <v>128047151</v>
       </c>
       <c r="B5" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,37 +986,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenflon Halån, Jmt</t>
+          <t>Finnboriset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519303</v>
+        <v>519394</v>
       </c>
       <c r="R5" t="n">
-        <v>7034701</v>
+        <v>7034721</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,17 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,33 +1057,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120467530</v>
+        <v>120467608</v>
       </c>
       <c r="B6" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519381</v>
+        <v>519308</v>
       </c>
       <c r="R6" t="n">
-        <v>7034632</v>
+        <v>7034634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120467541</v>
+        <v>120467529</v>
       </c>
       <c r="B7" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519253</v>
+        <v>519418</v>
       </c>
       <c r="R7" t="n">
-        <v>7034553</v>
+        <v>7034598</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1248,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,15 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120467531</v>
+        <v>120467530</v>
       </c>
       <c r="B8" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519310</v>
+        <v>519381</v>
       </c>
       <c r="R8" t="n">
-        <v>7034724</v>
+        <v>7034632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1350,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,37 +1377,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120467605</v>
+        <v>120467531</v>
       </c>
       <c r="B9" t="n">
-        <v>91367</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519237</v>
+        <v>519310</v>
       </c>
       <c r="R9" t="n">
-        <v>7034632</v>
+        <v>7034724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1448,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120467550</v>
+        <v>120467532</v>
       </c>
       <c r="B10" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519263</v>
+        <v>519303</v>
       </c>
       <c r="R10" t="n">
-        <v>7034520</v>
+        <v>7034701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1554,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,15 +1581,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120467534</v>
+        <v>120467533</v>
       </c>
       <c r="B11" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1616,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519291</v>
+        <v>519292</v>
       </c>
       <c r="R11" t="n">
-        <v>7034683</v>
+        <v>7034702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1656,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,15 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120467552</v>
+        <v>120467534</v>
       </c>
       <c r="B12" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519423</v>
+        <v>519291</v>
       </c>
       <c r="R12" t="n">
-        <v>7034575</v>
+        <v>7034683</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120467622</v>
+        <v>120467536</v>
       </c>
       <c r="B13" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1796,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1820,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519351</v>
+        <v>519272</v>
       </c>
       <c r="R13" t="n">
-        <v>7034684</v>
+        <v>7034688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1856,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120467548</v>
+        <v>120467537</v>
       </c>
       <c r="B14" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519263</v>
+        <v>519258</v>
       </c>
       <c r="R14" t="n">
-        <v>7034516</v>
+        <v>7034685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,15 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120467544</v>
+        <v>120467538</v>
       </c>
       <c r="B15" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2024,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519233</v>
+        <v>519248</v>
       </c>
       <c r="R15" t="n">
-        <v>7034494</v>
+        <v>7034653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2064,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,15 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120467545</v>
+        <v>120467539</v>
       </c>
       <c r="B16" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519234</v>
+        <v>519273</v>
       </c>
       <c r="R16" t="n">
-        <v>7034493</v>
+        <v>7034556</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2166,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,15 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120467539</v>
+        <v>120467540</v>
       </c>
       <c r="B17" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519273</v>
+        <v>519268</v>
       </c>
       <c r="R17" t="n">
-        <v>7034556</v>
+        <v>7034553</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2268,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,15 +2295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120467549</v>
+        <v>120467541</v>
       </c>
       <c r="B18" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519261</v>
+        <v>519253</v>
       </c>
       <c r="R18" t="n">
-        <v>7034519</v>
+        <v>7034553</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,15 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120467546</v>
+        <v>120467542</v>
       </c>
       <c r="B19" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519254</v>
+        <v>519242</v>
       </c>
       <c r="R19" t="n">
-        <v>7034484</v>
+        <v>7034507</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,15 +2499,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120467529</v>
+        <v>120467543</v>
       </c>
       <c r="B20" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,10 +2534,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519418</v>
+        <v>519241</v>
       </c>
       <c r="R20" t="n">
-        <v>7034598</v>
+        <v>7034507</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2574,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,15 +2601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120467538</v>
+        <v>120467544</v>
       </c>
       <c r="B21" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2636,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519248</v>
+        <v>519233</v>
       </c>
       <c r="R21" t="n">
-        <v>7034653</v>
+        <v>7034494</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2676,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,15 +2703,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120467608</v>
+        <v>120467545</v>
       </c>
       <c r="B22" t="n">
-        <v>79671</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2714,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2738,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519308</v>
+        <v>519234</v>
       </c>
       <c r="R22" t="n">
-        <v>7034634</v>
+        <v>7034493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2774,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,15 +2805,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120467623</v>
+        <v>120467546</v>
       </c>
       <c r="B23" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2816,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2840,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519234</v>
+        <v>519254</v>
       </c>
       <c r="R23" t="n">
-        <v>7034600</v>
+        <v>7034484</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,6 +2876,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,15 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120467536</v>
+        <v>120467547</v>
       </c>
       <c r="B24" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,10 +2942,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519272</v>
+        <v>519276</v>
       </c>
       <c r="R24" t="n">
-        <v>7034688</v>
+        <v>7034508</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +2982,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,15 +3009,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120467604</v>
+        <v>120467548</v>
       </c>
       <c r="B25" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,42 +3020,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519274</v>
+        <v>519263</v>
       </c>
       <c r="R25" t="n">
-        <v>7034556</v>
+        <v>7034516</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,7 +3084,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5 st +</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,15 +3111,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120467542</v>
+        <v>120467549</v>
       </c>
       <c r="B26" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,10 +3146,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519242</v>
+        <v>519261</v>
       </c>
       <c r="R26" t="n">
-        <v>7034507</v>
+        <v>7034519</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3186,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,15 +3213,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120467543</v>
+        <v>120467550</v>
       </c>
       <c r="B27" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519241</v>
+        <v>519263</v>
       </c>
       <c r="R27" t="n">
-        <v>7034507</v>
+        <v>7034520</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3288,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3445,15 +3315,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120467625</v>
+        <v>120467551</v>
       </c>
       <c r="B28" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,21 +3326,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3485,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519277</v>
+        <v>519324</v>
       </c>
       <c r="R28" t="n">
-        <v>7034510</v>
+        <v>7034551</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,6 +3386,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3547,15 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120467547</v>
+        <v>120467552</v>
       </c>
       <c r="B29" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519276</v>
+        <v>519423</v>
       </c>
       <c r="R29" t="n">
-        <v>7034508</v>
+        <v>7034575</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3627,7 +3492,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,15 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120467540</v>
+        <v>120467553</v>
       </c>
       <c r="B30" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3694,10 +3554,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519268</v>
+        <v>519489</v>
       </c>
       <c r="R30" t="n">
-        <v>7034553</v>
+        <v>7034525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3734,7 +3594,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3761,51 +3621,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128047142</v>
+        <v>120467604</v>
       </c>
       <c r="B31" t="n">
-        <v>75158</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Finnboriset, Jmt</t>
+          <t>Stenflon Halån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519270</v>
+        <v>519274</v>
       </c>
       <c r="R31" t="n">
-        <v>7034532</v>
+        <v>7034556</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3829,12 +3694,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>5 st +</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3843,56 +3713,56 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128047151</v>
+        <v>128047102</v>
       </c>
       <c r="B32" t="n">
-        <v>75175</v>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3900,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519394</v>
+        <v>519244</v>
       </c>
       <c r="R32" t="n">
-        <v>7034721</v>
+        <v>7034471</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3960,209 +3830,6 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>128047102</v>
-      </c>
-      <c r="B33" t="n">
-        <v>98489</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Finnboriset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>519244</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7034471</v>
-      </c>
-      <c r="S33" t="n">
-        <v>25</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>128047148</v>
-      </c>
-      <c r="B34" t="n">
-        <v>91482</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Finnboriset, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>519354</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7034679</v>
-      </c>
-      <c r="S34" t="n">
-        <v>25</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55922-2023 artfynd.xlsx
+++ b/artfynd/A 55922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467605</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047142</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467532</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467533</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467534</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467536</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467537</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467538</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467539</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467540</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467541</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467542</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467543</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467544</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467545</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2497,6 +2587,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467546</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467547</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467548</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467549</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467550</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3007,6 +3122,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467551</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3117,6 +3237,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467604</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3219,6 +3344,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047102</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3321,6 +3451,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047095</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3422,6 +3557,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128047151</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3524,6 +3664,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467529</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3626,6 +3771,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467530</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3728,6 +3878,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467552</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3830,8 +3985,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120467553</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>